--- a/docs/КАРТЫ — все таблицы.xlsx
+++ b/docs/КАРТЫ — все таблицы.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Приказы" sheetId="10" r:id="rId10"/>
     <sheet name="Утиль заданий" sheetId="11" r:id="rId11"/>
     <sheet name="Утиль арсенала" sheetId="12" r:id="rId12"/>
+    <sheet name="Курс наград" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -269,8 +270,21 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Курс наград</t>
+        </is>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">лист «Курс наград»: три числа из таблицы дизайнера, остальные — предположения</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C12"/>
 </worksheet>
 </file>
 
@@ -965,3264 +979,1706 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">№</t>
+          <t xml:space="preserve">Утиль-эффект</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Карта</t>
+          <t xml:space="preserve">Вид</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вид карты</t>
+          <t xml:space="preserve">Код эффекта</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Утиль-эффект</t>
+          <t xml:space="preserve">Параметры</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Код эффекта</t>
+          <t xml:space="preserve">Карт всего</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Параметры</t>
+          <t xml:space="preserve">Выработка</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Засада</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обеспечение</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Расплата</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экспансия</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начальные</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Номера карт</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o04</t>
+          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жила</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">exchange_science_or_market</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=barrage}</t>
+          <t xml:space="preserve">{amount=1}</t>
+        </is>
+      </c>
+      <c r="E2" s="2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o01, o68, o69, o42, o71, o21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o05</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выработка</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=withdraw}</t>
+          <t xml:space="preserve">energy_or_modules</t>
+        </is>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2">
+        <v>4</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o17, o11, o15, o12, o10, o02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o40</t>
+          <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ва-банк</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
+          <t xml:space="preserve">{coin=1}</t>
+        </is>
+      </c>
+      <c r="E4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2">
+        <v>6</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n1, n3, n5, n7, n9, n11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o08</t>
+          <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разведка недр</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
+          <t xml:space="preserve">{ammo=1}</t>
+        </is>
+      </c>
+      <c r="E5" s="2">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>6</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n2, n4, n6, n8, n10, n12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o01</t>
+          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полный залп</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{amount=1}</t>
+          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
+        </is>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o40, o08, o36, o64, o65</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o29</t>
+          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пустой двор</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=return_fire}</t>
+          <t xml:space="preserve">{kind=battle_first}</t>
+        </is>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o18, o20, o74, o75, o77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o03</t>
+          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Опорный пункт</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">{kind=return_fire}</t>
+        </is>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o29, o03, o63, o66</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o07</t>
+          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Засада</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">{kind=barrage}</t>
+        </is>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o04, o07, o70</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o27</t>
+          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">На чужом дворе</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=ricochet}</t>
+          <t xml:space="preserve">{ammo=1, order=operation}</t>
+        </is>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o33, o34, o06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o63</t>
+          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Голый запас</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=return_fire}</t>
+          <t xml:space="preserve">{kind=withdraw}</t>
+        </is>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o05, o67</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o33</t>
+          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Биржа</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{order=operation, ammo=1}</t>
+          <t xml:space="preserve">{kind=ricochet}</t>
+        </is>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o27, o76</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o36</t>
+          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Научный рывок</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
+          <t xml:space="preserve">{kind=evacuate_trophy}</t>
+        </is>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o25, o43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">o34</t>
+          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Научный отдел</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{order=operation, ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o64</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разнос трофеев</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o17</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Штаб на передовой</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o11</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Передовая база</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o18</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Полная нагрузка</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=battle_first}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o65</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Перестройка</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o15</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стройбум</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o12</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Наглая стройка</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o20</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Коммутация</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=battle_first}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o66</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Списание</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=return_fire}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o67</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разрядка</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=withdraw}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o10</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разоружение</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o06</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отгрузка</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{order=operation, ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o68</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Бронебой</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{amount=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o69</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зачистка гекса</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{amount=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o42</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разорение</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{amount=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o25</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Осада</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=evacuate_trophy}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o70</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Обесточивание</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=barrage}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o71</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Две войны</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{amount=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o72</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Против сильнейшего</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">heal_hex</t>
         </is>
       </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o21</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Первая кровь</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{amount=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o43</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Охота на сильного</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=evacuate_trophy}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o73</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Диверсия</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heal_hex</t>
-        </is>
-      </c>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o74</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Энергосеть</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=battle_first}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o75</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Рудный двор</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=battle_first}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o02</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Конвейер</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o76</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Расселение</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=ricochet}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">o77</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Растяжка</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=battle_first}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n1</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подъём</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 монета</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n2</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Первый боец</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n3</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Патроны</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 монета</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n4</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Первая сделка</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n5</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Коммутация</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 монета</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n6</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выход</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n7</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жила</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 монета</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n8</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Находка</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n9</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Первый шаг</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 монета</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n10</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Первый трофей</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n11</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Второй заход</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 монета</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n12</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В унисон</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1}</t>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o72, o73</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F53"/>
+  <autoFilter ref="A1:N14"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">№</t>
+          <t xml:space="preserve">Утиль-эффект</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Карта</t>
+          <t xml:space="preserve">Вид</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вид карты</t>
+          <t xml:space="preserve">Код эффекта</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Утиль-эффект</t>
+          <t xml:space="preserve">Параметры</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Код эффекта</t>
+          <t xml:space="preserve">Карт всего</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Параметры</t>
+          <t xml:space="preserve">Номера карт</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Низы этих карт</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_01</t>
+          <t xml:space="preserve">ДЕСАНТ: два разных войска на гекс без чужих жетонов</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Келемиевый дождь</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">landing</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">минус келемий - улучши 1 модуль</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gild_module</t>
-        </is>
+          <t xml:space="preserve">{count=2}</t>
+        </is>
+      </c>
+      <c r="E2" s="2">
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{pay=kelium, price=1}</t>
+          <t xml:space="preserve">a6_04, a6_22, a6_30</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">air_shields_own_hex, ground_ignores_buildings_in_maneuver, infantry_hp2_returns_on_damage</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_02</t>
+          <t xml:space="preserve">3 боеприпаса</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофейная команда</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">выполни действие Бой +1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{ammo=3}</t>
+        </is>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=combat, ammo=1}</t>
+          <t xml:space="preserve">a6_05, a6_35, bs2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_nuclear_strike_burn, spec_neutral_near_own_building, ammo_on_retaliation_kill</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_03</t>
+          <t xml:space="preserve">выполни действие Добыча</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофейная команда</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">забери жетон 1-го игрока и 1 монету у этого игрока</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grab_first_player</t>
-        </is>
+          <t xml:space="preserve">{action=mining}</t>
+        </is>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{now=true, steal_coin=1}</t>
+          <t xml:space="preserve">a6_07, a6_24, a6_36</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_move_miner_anywhere, kelium_instead_of_trophy, spec_release_garrison</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_04</t>
+          <t xml:space="preserve">построй любое здание за 1 монету</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Воздушный щит</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ДЕСАНТ: два разных войска на гекс без чужих жетонов</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">landing</t>
-        </is>
+          <t xml:space="preserve">{fixed_price=1, ops=1, action=build}</t>
+        </is>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{count=2}</t>
+          <t xml:space="preserve">a6_08, a6_26, a6_38</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">container_on_own_building_lost, plus1_storage_cell, spec_energy_on_card_free_attack</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_05</t>
+          <t xml:space="preserve">5 монет</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ядерный удар</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 боеприпаса</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
+          <t xml:space="preserve">{coin=5}</t>
+        </is>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ammo=3}</t>
+          <t xml:space="preserve">a6_10, a6_28, a6_39</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aircraft_slow_tough, science_trophy_to_coin, spec_boarding</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_06</t>
+          <t xml:space="preserve">выполни действие Снаряжение</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервный штаб</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">неограниченное число спец-действий до конца хода</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unlimited_spec</t>
-        </is>
+          <t xml:space="preserve">{action=assembly}</t>
+        </is>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">a6_14, a6_15, a6_40</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vehicle_fast_fragile, spec_move_energy_cube, repair_all_in_refresh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_07</t>
+          <t xml:space="preserve">минус келемий - улучши 1 модуль</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Геологоразведка</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gild_module</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">выполни действие Добыча</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{pay=kelium, price=1}</t>
+        </is>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=mining}</t>
+          <t xml:space="preserve">a6_01, a6_33</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_kelium_rain, repair_all_in_refresh</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_08</t>
+          <t xml:space="preserve">выполни действие Бой +1 боеприпас</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Страховая контора</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">построй любое здание за 1 монету</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{action=combat, ammo=1}</t>
+        </is>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{fixed_price=1, ops=1, action=build}</t>
+          <t xml:space="preserve">a6_02, a6_31</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_per_returned_enemy, infantry_hp2_returns_on_damage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_09</t>
+          <t xml:space="preserve">забери жетон 1-го игрока и 1 монету у этого игрока</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Страховая контора</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">grab_first_player</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">забери закрытую карту арсенала у противника</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">steal_arsenal_card</t>
-        </is>
+          <t xml:space="preserve">{now=true, steal_coin=1}</t>
+        </is>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">a6_03, a6_19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_per_returned_enemy, towers_fast_fragile</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_10</t>
+          <t xml:space="preserve">неограниченное число спец-действий до конца хода</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тяжёлое крыло</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">unlimited_spec</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 монет</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{coin=5}</t>
+          <t xml:space="preserve">a6_06, a6_11</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kelium_ignores_block, two_spec_without_security</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_11</t>
+          <t xml:space="preserve">забери закрытую карту арсенала у противника</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оперативный отдел</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">steal_arsenal_card</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">неограниченное число спец-действий до конца хода</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unlimited_spec</t>
-        </is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">a6_09, a6_20</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">container_on_own_building_lost, towers_fast_fragile</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_12</t>
+          <t xml:space="preserve">поменяй свою карту приказа из руки на одну из сброса</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оперативный отдел</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">swap_order_card</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">поменяй свою карту приказа из руки на одну из сброса</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swap_order_card</t>
-        </is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">a6_12, a6_16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">two_spec_without_security, bottom_order_instead_of_top</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_13</t>
+          <t xml:space="preserve">удали установленную карту арсенала у противника</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Облегчённая броня</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">discard_enemy_arsenal</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">удали установленную карту арсенала у противника</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">discard_enemy_arsenal</t>
-        </is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">a6_13, a6_21</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vehicle_fast_fragile, air_gives_range_two</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_14</t>
+          <t xml:space="preserve">продвинься на одном треке в Науке, плати монетами вместо трофеев</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Облегчённая броня</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">выполни действие Снаряжение</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{action=science, pay_with_coin=true}</t>
+        </is>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=assembly}</t>
+          <t xml:space="preserve">a6_17, a6_23</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bottom_order_instead_of_top, kelium_instead_of_trophy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_15</t>
+          <t xml:space="preserve">один обмен на рынке не тратя келемий</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диспетчер энергии</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">выполни действие Снаряжение</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{action=market, free_deals=1}</t>
+        </is>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=assembly}</t>
+          <t xml:space="preserve">a6_18, a6_32</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_kelium_on_energy_cell, pay_energy_with_coin</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_16</t>
+          <t xml:space="preserve">забери у противника до 2 карт заданий</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Двойной протокол</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">steal_objective_cards</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">поменяй свою карту приказа из руки на одну из сброса</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swap_order_card</t>
-        </is>
+          <t xml:space="preserve">{count=2}</t>
+        </is>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">a6_25, a6_29</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_boarding, science_trophy_to_coin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_17</t>
+          <t xml:space="preserve">воспользуйся одной сделкой с любой сброшенной карты рынка</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Двойной протокол</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">market_card_from_discard</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">продвинься на одном треке в Науке, плати монетами вместо трофеев</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=science, pay_with_coin=true}</t>
+          <t xml:space="preserve">a6_27, a6_34</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus1_storage_cell, counter_battle_for_ammo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_18</t>
+          <t xml:space="preserve">выполни Стройку</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кристальный реактор</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">один обмен на рынке не тратя келемий</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{action=build}</t>
+        </is>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=market, free_deals=1}</t>
+          <t xml:space="preserve">bs5, bs8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coin_on_kill, build_on_adjacent_with_own_units</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_19</t>
+          <t xml:space="preserve">три СПЕЦ-действия в этот ход</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Передвижные вышки</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">three_spec_actions</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">забери жетон 1-го игрока и 1 монету у этого игрока</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grab_first_player</t>
-        </is>
+          <t xml:space="preserve">{spec_actions=3}</t>
+        </is>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{now=true, steal_coin=1}</t>
+          <t xml:space="preserve">a6_37</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kelium_instead_of_ammo_in_operation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_20</t>
+          <t xml:space="preserve">выполни Рынок</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Передвижные вышки</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">забери закрытую карту арсенала у противника</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">steal_arsenal_card</t>
-        </is>
+          <t xml:space="preserve">{action=market}</t>
+        </is>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">bs1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card_is_energy_source_upkeep</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_21</t>
+          <t xml:space="preserve">2 келемия</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наводчик</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">удали установленную карту арсенала у противника</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">discard_enemy_arsenal</t>
-        </is>
+          <t xml:space="preserve">{kelium=2}</t>
+        </is>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">bs3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_loot_enemy_building_hex</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_22</t>
+          <t xml:space="preserve">3 карты задания</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Штурмовые тропы</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ДЕСАНТ: два разных войска на гекс без чужих жетонов</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">landing</t>
-        </is>
+          <t xml:space="preserve">{objective_cards=3}</t>
+        </is>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{count=2}</t>
+          <t xml:space="preserve">bs4</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_draw_two_objectives_keep_one</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_23</t>
+          <t xml:space="preserve">замени 1 карту приказа в руке на карту из своего сброса</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кристальная лаборатория</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">swap_order_card</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">продвинься на одном треке в Науке, плати монетами вместо трофеев</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=science, pay_with_coin=true}</t>
+          <t xml:space="preserve">bs6</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">economy_plus1_hp_returns_on_damage</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6_24</t>
+          <t xml:space="preserve">выполни Добычу</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кристальная лаборатория</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">обычная</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">выполни действие Добыча</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
+          <t xml:space="preserve">{action=mining}</t>
+        </is>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=mining}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_25</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Абордаж</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">забери у противника до 2 карт заданий</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">steal_objective_cards</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{count=2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Перевалочная база</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">построй любое здание за 1 монету</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{fixed_price=1, ops=1, action=build}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_27</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Перевалочная база</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">воспользуйся одной сделкой с любой сброшенной карты рынка</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market_card_from_discard</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_28</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скупка металла</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 монет</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_29</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скупка металла</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">забери у противника до 2 карт заданий</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">steal_objective_cards</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{count=2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_30</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ударная пехота</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ДЕСАНТ: два разных войска на гекс без чужих жетонов</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">landing</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{count=2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_31</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ударная пехота</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни действие Бой +1 боеприпас</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=combat, ammo=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_32</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Аварийное питание</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">один обмен на рынке не тратя келемий</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=market, free_deals=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_33</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ремонтная база</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">минус келемий - улучши 1 модуль</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gild_module</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{pay=kelium, price=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_34</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ответный огонь</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">воспользуйся одной сделкой с любой сброшенной карты рынка</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market_card_from_discard</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_35</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подрядчик</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпаса</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_36</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Комендатура</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни действие Добыча</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=mining}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_37</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Кристальный боезапас</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">три СПЕЦ-действия в этот ход</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">three_spec_actions</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{spec_actions=3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_38</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разрядник</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">построй любое здание за 1 монету</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{fixed_price=1, ops=1, action=build}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_39</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Абордаж</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 монет</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a6_40</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ремонтная база</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обычная</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни действие Снаряжение</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=assembly}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs1</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Полевой генератор</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни Рынок</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=market}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs2</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ответный залп</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпаса</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs3</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мародёрка</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 келемия</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kelium=2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs4</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Штабная почта</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 карты задания</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{objective_cards=3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs5</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Премия за голову</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни Стройку</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=build}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs6</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Аварийные щиты</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">замени 1 карту приказа в руке на карту из своего сброса</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swap_order_card</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">bs7</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Переформирование</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни Добычу</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=mining}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bs8</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Вольная застройка</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">начальная</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">выполни Стройку</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=build}</t>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spec_swap_ground_unit</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F49"/>
+  <autoFilter ref="A1:G25"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вид награды</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оценка</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откуда взято</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">монеты</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">таблица дизайнера: 3 монеты = цена 3.0, 4 монеты = 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">боеприпасы</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">таблица дизайнера: 2 монеты + 1 боеприпас = 3.25, 3 боеприпаса = 3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карты задания</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">таблица дизайнера: 2 монеты + 1 задание = 3.6, 2 задания = 3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">трофеи</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ по печатному курсу: в Научном отделе 2 трофея = карта арсенала, 2 трофея = позолота модуля</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карта арсенала</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ: ровно 2 трофея по обмену Научного отдела</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карта арсенала НА ВЫБОР из открытых</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ: та же карта, но НА ВЫБОР из открытых — дороже слепой на половину трофея</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">жетон модуля</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ: награда 2-й и 3-й ступени трека, то есть вровень с картой арсенала</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">келемий</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ по печатному курсу рынка: 1 келемий = 3 монеты</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">жетон хранилища</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ: ячейка хранилища или энергия ЦУ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">победные очки</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПРЕДПОЛОЖЕНИЕ: победное очко при типичном итоге партии 8-12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
 </worksheet>
 </file>
 
@@ -4232,12 +2688,25 @@
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="34" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="44" customWidth="1"/>
+    <col min="22" max="22" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4253,35 +2722,100 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Семейство</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Природа</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Условие</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">монеты</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">боеприпасы</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карты задания</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">трофеи</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карта арсенала</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">жетон модуля</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОЦЕНКА награды</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Усиление</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Награда</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Усиленная награда</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">усил.: монеты</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">усил.: боеприпасы</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">усил.: карты задания</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">усил.: трофеи</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">усил.: карта арсенала</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">усил.: жетон модуля</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОЦЕНКА с усилением</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Утиль</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Описание</t>
         </is>
@@ -4300,35 +2834,54 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Выработка</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Оба примыкают к большим зарождениям</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля атаки</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">атаки</t>
+        </is>
+      </c>
+      <c r="T2" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям, — награда 3 монеты. Если оба примыкают к большим зарождениям, условие усилено: жетон модуля атаки. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
         </is>
@@ -4347,35 +2900,54 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Выработка</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД забери последний келемий с зарождения</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ты исчерпал зарождение - оно ушло с поля</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля сборки</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сборки</t>
+        </is>
+      </c>
+      <c r="T3" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД забери последний келемий с зарождения — награда 3 монеты. Если ты исчерпал зарождение и оно ушло с поля, условие усилено: жетон модуля сборки. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
         </is>
@@ -4394,35 +2966,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Выработка</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей одновременно ноль монет и ноль боеприпасов</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
+        <v>3.25</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Не имей даже келемий</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, боеприпасы</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2">
+        <v>5.25</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей одновременно ноль монет и ноль боеприпасов — награда 2 монеты и 1 боеприпас. Не имей даже келемий, и условие усилено: 1 трофей. Ва-банк играют только на голом столе.</t>
         </is>
@@ -4441,27 +3032,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Выработка</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками)</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, боеприпасы</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
+        <v>3.25</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2">
+        <v>3.25</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками) — награда 2 монеты и 1 боеприпас. Усиления у карты нет: три контейнера за ход и так работа всей смены. Каждый добытчик в Добыче выбирает одно: келемий или контейнер.</t>
         </is>
@@ -4480,35 +3092,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Выработка</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД произведи только боеприпасы и ни одного войска</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Эти здания - завод и авиабаза</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, карты задания</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД произведи только боеприпасы и ни одного войска — награда 2 монеты и 1 карта задания. Если эти здания - завод и авиабаза, условие усилено: 1 карта арсенала. Ход без единого нового войска — цена полного залпа.</t>
         </is>
@@ -4527,35 +3158,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Засада</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей два своих войска на гексах, где нет твоих зданий</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Четыре - и все стоят на разных гексах</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, карты задания</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля сборки</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сборки</t>
+        </is>
+      </c>
+      <c r="T7" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей два своих войска на гексах, где нет твоих зданий, — награда 2 монеты и 1 карта задания. Если таких войск четыре и все стоят на разных гексах, условие усилено: жетон модуля сборки. Войско без своего здания рядом умрёт первым — зато не даром.</t>
         </is>
@@ -4574,35 +3226,52 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Засада</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле 2 свои вышки на разных гексах (обе не на гексе с ЦУ)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Одна из вышек стоит на гексе с жетонами врага</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпасы</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2">
+        <v>2</v>
+      </c>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2">
+        <v>7.75</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле 2 свои вышки на разных гексах, и обе не на гексе с ЦУ, — награда 3 боеприпаса. Если одна из вышек стоит на гексе с жетонами врага, условие усилено: 2 трофея. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
         </is>
@@ -4621,35 +3290,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Засада</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Держи так сразу два своих войска</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпасы</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2">
+        <v>7.75</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага, — награда 3 боеприпаса. Держи так сразу два войска, и условие усилено: 1 карта арсенала. Гарнизон в здании не виден до первого выстрела.</t>
         </is>
@@ -4668,35 +3354,52 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Засада</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей своё войско на гексе, где есть здания врага</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на одном таком гексе два своих войска</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпасы</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2">
+        <v>1</v>
+      </c>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2">
+        <v>7.75</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей своё войско на гексе, где есть здания врага, — награда 3 боеприпаса. Имей на одном таком гексе два своих войска, и условие усилено: 1 карта арсенала. Двор чужой, а гекс общий: здание закрывает только свои стенки, и войти во двор можно, пока в нём есть свободный сектор.</t>
         </is>
@@ -4715,35 +3418,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Засада</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей в запасе 0 войск одного вида</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
+        <v>4.1</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Двух видов</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 боеприпасы, карты задания</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2">
+        <v>2</v>
+      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей в запасе 0 войск одного вида — награда 2 боеприпаса и 1 карта задания. Если так стоят сразу два рода, условие усилено: 2 трофея. Вывести род целиком значит подставить его целиком: в запасе не осталось никого, кем заменить убитого.</t>
         </is>
@@ -4762,27 +3484,46 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Обеспечение</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся двумя разными предложениями Рынка</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
+      <c r="F12" s="2">
+        <v>3</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся двумя разными предложениями Рынка. Награда: 3 монеты. Напечатанные курсы планшета и предложения карты рынка считаются по отдельности. Усиления у карты нет.</t>
         </is>
@@ -4801,35 +3542,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Обеспечение</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Дойди до второго шага хотя бы на одном треке технологий</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Стой на втором шаге сразу на двух треках</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2">
+        <v>1</v>
+      </c>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Дойди до второго шага хотя бы на одном треке технологий — награда 3 монеты. Стой на втором шаге сразу на двух треках, и условие усилено: 1 карта арсенала. Второй шаг — первое место, где трек начинает платить очками.</t>
         </is>
@@ -4848,27 +3606,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Обеспечение</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">монеты, 2 боеприпасы</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки. Награда: 1 монета и 2 боеприпаса. Шаг по треку и каждый обмен трофеев на планшете технологий считаются отдельным предложением; обменов на планшете три, значит три предложения — это ровно все они за один ход. Усиления у карты нет.</t>
         </is>
@@ -4887,35 +3666,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Обеспечение</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД сдай трофеи на ДВУХ разных треках технологий</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
+        <v>2</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На трёх треках</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 карты задания</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено: 1 карта арсенала. Одно действие Науки берёт сколько угодно разных треков, по шагу на каждом, — но каждый шаг оплачивается трофеями отдельно.</t>
         </is>
@@ -4934,35 +3730,52 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Твоих зданий вокруг чужого ЦУ два, и стоят они на разных гексах</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2">
+        <v>2</v>
+      </c>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника, — награда 3 монеты. Если таких твоих зданий два и стоят они на разных гексах, условие усилено: 2 трофея. Подобраться стройкой к чужому штабу дороже, чем кажется: туда ещё надо дойти, и там по тебе будут бить.</t>
         </is>
@@ -4981,35 +3794,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД построй свое здание на гексе, соседнем с гексом, где есть войска врага</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На том же соседнем гексе есть здание врага</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2">
+        <v>1</v>
+      </c>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда 3 монеты. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 карта арсенала. Передовая база строится под огнём — потому и платит.</t>
         </is>
@@ -5028,35 +3858,52 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Все твои здания, требующие энергию, запитаны (не менее 3)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Не менее 4 зданий</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2">
+        <v>1</v>
+      </c>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Все твои здания, требующие энергию, запитаны, и таких зданий не менее трёх, — награда 3 монеты. Не менее четырёх зданий — условие усилено: 1 карта арсенала. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
         </is>
@@ -5075,35 +3922,54 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД снеси своё здание и построй другое</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Построенное встало на тот же гекс, где стояло снесённое</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, карты задания</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД снеси своё здание и построй другое — награда 2 монеты и 1 карта задания. Если построенное встало на тот же гекс, где стояло снесённое, условие усилено: 1 трофей. Здание не переезжает: его сносят и ставят заново, и обе операции стоят действия.</t>
         </is>
@@ -5122,35 +3988,52 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД построй 2 здания на разных гексах</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2">
+        <v>3</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 здания на разных и несоседних между собой гексах</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпасы</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2">
+        <v>1</v>
+      </c>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2">
+        <v>5.75</v>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД построй 2 здания на разных гексах — награда 3 боеприпаса. Построй 3 здания на разных и несоседних между собой гексах, и условие усилено: 1 трофей. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
         </is>
@@ -5169,35 +4052,52 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На этом гексе два и более жетонов врага</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2">
+        <v>2</v>
+      </c>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага, — награда 4 монеты. Если на этом гексе два и более жетонов врага, условие усилено: 2 трофея. Стройка под чужим стволом — заявка, а не расчёт.</t>
         </is>
@@ -5216,35 +4116,54 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Развёртывание</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на двух зданиях - источниках энергии ровно один свободный кубик</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На трех источниках энергии</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля сборки</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сборки</t>
+        </is>
+      </c>
+      <c r="T22" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на двух зданиях - источниках энергии ровно один свободный кубик — награда 4 монеты. На трёх источниках энергии условие усилено: жетон модуля сборки. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному неудобно намеренно.</t>
         </is>
@@ -5263,27 +4182,52 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Расплата</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">жертва</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Сбрось карту арсенала</t>
         </is>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, боеприпасы, жетон модуля атаки</t>
-        </is>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="F23" s="2">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">атаки</t>
+        </is>
+      </c>
+      <c r="L23" s="2">
+        <v>7.25</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2">
+        <v>7.25</v>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Сбрось карту арсенала — награда 2 монеты и 1 боеприпас и жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
         </is>
@@ -5302,27 +4246,50 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Расплата</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">жертва</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Сдай в общий запас 2 боеприпаса</t>
         </is>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, карты задания, карта арсенала</t>
-        </is>
+      <c r="F24" s="2">
+        <v>2</v>
       </c>
       <c r="G24" s="2"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Сдай в общий запас 2 боеприпаса — награда 2 монеты и 1 карта задания и 1 карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
         </is>
@@ -5341,35 +4308,54 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Расплата</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">жертва</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Верни в запас 2 своих войска с поля</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2">
+        <v>3</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Технику и/или авиацию - и с одного гекса</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 боеприпасы</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля сборки</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сборки</t>
+        </is>
+      </c>
+      <c r="T25" s="2">
+        <v>7.75</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Верни в запас 2 своих войска с поля — награда 3 боеприпаса. Если это техника и/или авиация и оба жетона с одного гекса, условие усилено: жетон модуля сборки. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
         </is>
@@ -5388,27 +4374,48 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Расплата</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">жертва</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Сдай два своих неоткрытых контейнера</t>
         </is>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты, 2 трофеи</t>
-        </is>
+      <c r="F26" s="2">
+        <v>3</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Сдай два своих неоткрытых контейнера — награда 3 монеты и 2 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
         </is>
@@ -5427,35 +4434,52 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь технику или авиацию врага</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">и еще 2 жетона любого врага</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2">
+        <v>1</v>
+      </c>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь технику или авиацию врага — награда 4 монеты. Если снял ещё два любых чужих жетона, условие усилено: карта арсенала. Техника и авиация дороже прочего и стоят дальше от чужих стен: до них ещё надо дотянуться.</t>
         </is>
@@ -5474,35 +4498,54 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2">
+        <v>4</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">их на этом гексе не менее 3</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля атаки</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">атаки</t>
+        </is>
+      </c>
+      <c r="T28" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе — награда 4 монеты. Если их там было не меньше трёх, условие усилено: жетон модуля атаки. Вычистить гекс целиком — работа не одного выстрела: здание закрывает гекс, и снимать приходится по очереди.</t>
         </is>
@@ -5521,35 +4564,54 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь добытчик противника</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2">
+        <v>4</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Этот добытчик был полностью запитан и примыкал к келемию</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля атаки</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">атаки</t>
+        </is>
+      </c>
+      <c r="T29" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь добытчик противника — награда 4 монеты. Если этот добытчик был полностью запитан и примыкал к келемию, условие усилено: жетон модуля атаки. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи — а работающий на полную вдвое дороже.</t>
         </is>
@@ -5568,35 +4630,54 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов жетон врага</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2">
+        <v>4</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">два жетона, один из них - добытчик</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля атаки</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">атаки</t>
+        </is>
+      </c>
+      <c r="T30" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов жетон врага — награда 4 монеты. Если их два и один из них добытчик, условие усилено: жетон модуля атаки. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
         </is>
@@ -5615,35 +4696,54 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов два жетона врага</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2">
+        <v>4</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Один из них — энергостанция</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля сборки</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сборки</t>
+        </is>
+      </c>
+      <c r="T31" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов два жетона врага — награда 4 монеты. Если один из них энергостанция, условие усилено: жетон модуля сборки. Энергостанция питает всё остальное, поэтому её снос стоит противнику дороже собственной цены.</t>
         </is>
@@ -5662,35 +4762,54 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов жетоны ДВУХ разных противников</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2">
+        <v>4</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">И оба этих жетона — здания</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля сборки</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сборки</t>
+        </is>
+      </c>
+      <c r="T32" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов жетоны двух разных противников — награда 4 монеты. Если оба этих жетона здания, условие усилено: жетон модуля сборки. Единственная карта колоды, которую нельзя закрыть, воюя с одним соседом.</t>
         </is>
@@ -5709,35 +4828,54 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтоженный жетон был техникой или авиацией</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, карты задания</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2">
+        <v>1</v>
+      </c>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя, — награда 2 монеты и 1 карта задания. Если уничтоженный был техникой или авиацией, условие усилено: 1 трофей. Бить сильнейшего значит получить сдачи, и карта платит именно за это.</t>
         </is>
@@ -5756,35 +4894,54 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь два жетона противника</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД у одного из уничтоженных прочность была 2 или больше</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 монеты</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">жетон модуля атаки</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">атаки</t>
+        </is>
+      </c>
+      <c r="T34" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь два жетона противника — награда 4 монеты. Если у одного из них прочность была 2 или больше, условие усилено: жетон модуля атаки. Первая кровь считается по двум, а не по одному.</t>
         </is>
@@ -5803,35 +4960,54 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2">
+        <v>2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2">
+        <v>4.1</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтоженный жетон был зданием</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 боеприпасы, карты задания</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2">
+        <v>1</v>
+      </c>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда 2 боеприпаса и 1 карта задания. Если уничтоженный жетон был зданием, условие усилено: 1 трофей. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
         </is>
@@ -5850,35 +5026,54 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Устранение</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь энергостанцию противника</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2">
+        <v>4.1</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Это была энергостанция 3 или 4 уровня.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 боеприпасы, карты задания</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2">
+        <v>2</v>
+      </c>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь энергостанцию противника — награда 2 боеприпаса и 1 карта задания. Если это была энергостанция третьего или четвёртого уровня, условие усилено: 2 трофея. Крупные энергостанции стоят в глубине, и лезть за ними опасно.</t>
         </is>
@@ -5897,27 +5092,46 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Экспансия</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле все свои 4 здания энергостанций</t>
         </is>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 карты задания</t>
-        </is>
-      </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="2">
+        <v>2</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле все свои 4 здания энергостанций — награда 2 карты задания. Полный комплект источников на поле — лучшая мишень в партии: их нечем прикрыть и негде спрятать.</t>
         </is>
@@ -5936,27 +5150,46 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Экспансия</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле все свои 4 здания добытчиков</t>
         </is>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 карты задания</t>
-        </is>
-      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="2">
+        <v>2</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле все свои 4 здания добытчиков — награда 2 карты задания. Разложил всё, чем добываешь, — держи оборону или жги карту: у добытчика прочность один.</t>
         </is>
@@ -5975,35 +5208,54 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Экспансия</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">происшествие</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД найми два войска разных родов</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Среди нанятых есть авиация и нет ни одной вышки</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 монеты, карты задания</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2">
+        <v>2</v>
+      </c>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД найми два войска разных родов — награда 2 монеты и 1 карта задания. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 2 трофея. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
         </is>
@@ -6022,35 +5274,52 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Экспансия</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Займи 4 разных гекса войсками хотя бы 2 видов</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">6 гексов</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 монеты</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 трофеи</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2">
+        <v>2</v>
+      </c>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Займи 4 разных гекса войсками хотя бы 2 видов — награда 3 монеты. 6 гексов, и условие усилено: 2 трофея. Растянуться по полю выгодно и опасно разом: где тонко, там и порвут.</t>
         </is>
@@ -6069,42 +5338,61 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Экспансия</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">состояние</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Займи войсками 5 разных гексов</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2">
+        <v>2</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2">
+        <v>4.1</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На 2 из них есть здания противника</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 боеприпасы, карты задания</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта арсенала</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2">
+        <v>1</v>
+      </c>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Займи войсками 5 разных гексов — награда 2 боеприпаса и 1 карта задания. Если на двух из них есть здания противника, условие усилено: 1 карта арсенала. Гекс с чужим зданием закрыт: стоять там можно, бить оттуда — только по зданиям и вышкам.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I41"/>
+  <autoFilter ref="A1:V41"/>
 </worksheet>
 </file>
 
@@ -6113,11 +5401,17 @@
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="70" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
+    <col min="13" max="13" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6143,15 +5437,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Награда</t>
+          <t xml:space="preserve">монеты</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">боеприпасы</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карты задания</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">трофеи</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">карта арсенала</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">жетон модуля</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОЦЕНКА награды</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Утиль</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Описание</t>
         </is>
@@ -6178,17 +5502,25 @@
           <t xml:space="preserve">Имей на поле не меньше трёх своих зданий, считая ЦУ</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле не меньше трёх своих зданий, считая ЦУ, — награда трофей и карта задания. Считается и ЦУ, поэтому от подготовки до выполнения ровно две стройки.</t>
         </is>
@@ -6215,17 +5547,25 @@
           <t xml:space="preserve">В ЭТОТ ХОД найми войско любого рода, кроме вышки</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД найми войско любого рода, кроме вышки, — награда трофей и карта задания. Вышка не считается: её ЦУ собирает даром, и наймом это назвать нельзя.</t>
         </is>
@@ -6252,17 +5592,25 @@
           <t xml:space="preserve">Имей не меньше трёх боеприпасов</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей не меньше трёх боеприпасов — награда трофей и карта задания. Порог три, а не два: один боеприпас у тебя уже есть с подготовки.</t>
         </is>
@@ -6289,17 +5637,25 @@
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся предложением карты сделок на рынке</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся предложением карты сделок на рынке — награда трофей и карта задания. Напечатанный курс не подходит: карта требует именно предложения карты сделок.</t>
         </is>
@@ -6326,17 +5682,25 @@
           <t xml:space="preserve">Имей на поле запитанное здание, стоящее не на гексе с твоим ЦУ</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле запитанное здание, стоящее не на гексе с твоим ЦУ, — награда трофей и карта задания. Энергия до соседнего гекса сама не дотянется: её надо туда перекинуть Сменой энергии.</t>
         </is>
@@ -6363,17 +5727,25 @@
           <t xml:space="preserve">Имей на поле своё войско на расстоянии двух и больше гексов от гекса с твоим ЦУ</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле своё войско на расстоянии двух и больше гексов от гекса с твоим ЦУ — награда трофей и карта задания. Вышка неподвижна, так что выйти придётся кем-то живым.</t>
         </is>
@@ -6400,17 +5772,25 @@
           <t xml:space="preserve">Имей не меньше трёх келемия</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей не меньше трёх келемия — награда трофей и карта задания. Келемий равен победному очку, поэтому держать его дорого, а тратить жалко.</t>
         </is>
@@ -6437,17 +5817,25 @@
           <t xml:space="preserve">Имей у себя не меньше двух неоткрытых контейнеров</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей у себя не меньше двух неоткрытых контейнеров — награда трофей и карта задания. Вскрытый контейнер сразу уходит, так что придётся терпеть и не открывать.</t>
         </is>
@@ -6474,17 +5862,25 @@
           <t xml:space="preserve">Стой хотя бы на первом шаге любого трека технологий</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Стой хотя бы на первом шаге любого трека технологий — награда трофей и карта задания. За действие Наука больше одного шага на трек не сделать, поэтому начинают все с одного и того же.</t>
         </is>
@@ -6511,17 +5907,25 @@
           <t xml:space="preserve">Имей среди уничтоженных жетонов хотя бы один жетон</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов хотя бы один жетон — награда трофей и карта задания. Трофей берут только с боя, поэтому карта платит за первый настоящий выстрел.</t>
         </is>
@@ -6548,17 +5952,25 @@
           <t xml:space="preserve">В ЭТОТ ХОД получи действие с нижнего приказа своей карты приказа</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД получи действие с нижнего приказа своей карты приказа — награда трофей и карта задания. Нижний приказ открывается не всегда, так что карту держат до подходящего раунда.</t>
         </is>
@@ -6585,24 +5997,32 @@
           <t xml:space="preserve">В ЭТОТ ХОД сыграй верхом тот же приказ, что и другой игрок</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">трофеи, карты задания</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД сыграй верхом тот же приказ, что и другой игрок, — награда трофей и карта задания. Совпавший приказ не срабатывает, так что эта карта — плата за потерянное действие.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:M13"/>
 </worksheet>
 </file>
 

--- a/docs/КАРТЫ — все таблицы.xlsx
+++ b/docs/КАРТЫ — все таблицы.xlsx
@@ -133,7 +133,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.17.0</t>
+          <t xml:space="preserve">1.18.0</t>
         </is>
       </c>
     </row>
@@ -148,7 +148,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.17.0</t>
+          <t xml:space="preserve">1.18.0</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.42.0</t>
+          <t xml:space="preserve">1.45.0</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1080,39 +1080,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">exchange_science_or_market</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{amount=1}</t>
+          <t xml:space="preserve">{action=combat}</t>
         </is>
       </c>
       <c r="E2" s="2">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2">
+        <v>2</v>
+      </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
       <c r="K2" s="2">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o01, o68, o69, o42, o71, o21</t>
+          <t xml:space="preserve">o29, o03, o10, o68, o69, o42, o25, o02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1122,271 +1126,279 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="D3" s="2"/>
+          <t xml:space="preserve">free_action</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{action=movement}</t>
+        </is>
+      </c>
       <c r="E3" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2">
-        <v>4</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2">
+        <v>3</v>
+      </c>
       <c r="L3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o17, o11, o15, o12, o10, o02</t>
+          <t xml:space="preserve">o63, o65, o15, o70, o71, o72, o74, o75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 монета</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ресурс (СПЕЦ)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{coin=1}</t>
-        </is>
-      </c>
+          <t xml:space="preserve">energy_or_modules</t>
+        </is>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2">
-        <v>6</v>
-      </c>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">n1, n3, n5, n7, n9, n11</t>
+          <t xml:space="preserve">o04, o05, o64, o12, o20, o06, o76</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 боеприпас</t>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ресурс (СПЕЦ)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gain</t>
+          <t xml:space="preserve">deploy_units</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ammo=1}</t>
+          <t xml:space="preserve">{count=1}</t>
         </is>
       </c>
       <c r="E5" s="2">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>3</v>
+      </c>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
       <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>6</v>
-      </c>
+      <c r="M5" s="2"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">n2, n4, n6, n8, n10, n12</t>
+          <t xml:space="preserve">o08, o36, o34, o17, o11, o18, o21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">действие (СПЕЦ)</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">free_action</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
+          <t xml:space="preserve">{coin=1}</t>
         </is>
       </c>
       <c r="E6" s="2">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="M6" s="2">
+        <v>6</v>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o40, o08, o36, o64, o65</t>
+          <t xml:space="preserve">n1, n3, n5, n7, n9, n11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
+          <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">в моменте (реакция)</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reaction</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=battle_first}</t>
+          <t xml:space="preserve">{ammo=1}</t>
         </is>
       </c>
       <c r="E7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2">
-        <v>2</v>
-      </c>
+      <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>6</v>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o18, o20, o74, o75, o77</t>
+          <t xml:space="preserve">n2, n4, n6, n8, n10, n12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
+          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">в моменте (реакция)</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reaction</t>
+          <t xml:space="preserve">gain</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=return_fire}</t>
+          <t xml:space="preserve">{order=operation, ammo=1}</t>
         </is>
       </c>
       <c r="E8" s="2">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o29, o03, o63, o66</t>
+          <t xml:space="preserve">o40, o33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
+          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">в моменте (реакция)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reaction</t>
+          <t xml:space="preserve">exchange_science_or_market</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=barrage}</t>
+          <t xml:space="preserve">{amount=1}</t>
         </is>
       </c>
       <c r="E9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1397,56 +1409,52 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o04, o07, o70</t>
+          <t xml:space="preserve">o01, o73</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
+          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ресурс (СПЕЦ)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gain</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{ammo=1, order=operation}</t>
-        </is>
-      </c>
+          <t xml:space="preserve">heal_hex</t>
+        </is>
+      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2">
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o33, o34, o06</t>
+          <t xml:space="preserve">o43, o77</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
+          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1461,34 +1469,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=withdraw}</t>
+          <t xml:space="preserve">{kind=ricochet}</t>
         </is>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
-      </c>
-      <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
+      <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o05, o67</t>
+          <t xml:space="preserve">o07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
+          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1503,11 +1509,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=ricochet}</t>
+          <t xml:space="preserve">{kind=return_fire}</t>
         </is>
       </c>
       <c r="E12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2">
@@ -1517,20 +1523,18 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2">
-        <v>1</v>
-      </c>
+      <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o27, o76</t>
+          <t xml:space="preserve">o27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
+          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1545,61 +1549,65 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=evacuate_trophy}</t>
+          <t xml:space="preserve">{kind=barrage}</t>
         </is>
       </c>
       <c r="E13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2">
-        <v>2</v>
-      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o25, o43</t>
+          <t xml:space="preserve">o66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
+          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">действие (СПЕЦ)</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">heal_hex</t>
-        </is>
-      </c>
-      <c r="D14" s="2"/>
+          <t xml:space="preserve">reaction</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{kind=evacuate_trophy}</t>
+        </is>
+      </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2">
-        <v>2</v>
-      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">o72, o73</t>
+          <t xml:space="preserve">o67</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2705,18 @@
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="34" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="34" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="44" customWidth="1"/>
-    <col min="22" max="22" width="70" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="44" customWidth="1"/>
+    <col min="24" max="24" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2757,65 +2767,75 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта арсенала</t>
+          <t xml:space="preserve">келемий</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">жетон модуля</t>
+          <t xml:space="preserve">action</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">spec_actions</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">ОЦЕНКА награды</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Усиление</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">усил.: монеты</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">усил.: боеприпасы</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">усил.: карты задания</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">усил.: трофеи</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">усил.: карта арсенала</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">усил.: жетон модуля</t>
+          <t xml:space="preserve">усил.: келемий</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОЦЕНКА с усилением</t>
+          <t xml:space="preserve">усил.: action</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">усил.: spec_actions</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОЦЕНКА лучшей из двух</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Утиль</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Описание</t>
         </is>
@@ -2847,43 +2867,45 @@
           <t xml:space="preserve">Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям</t>
         </is>
       </c>
-      <c r="F2" s="2">
-        <v>3</v>
-      </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mining</t>
+        </is>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Оба примыкают к большим зарождениям</t>
         </is>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">атаки</t>
-        </is>
-      </c>
-      <c r="T2" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям, — награда 3 монеты. Если оба примыкают к большим зарождениям, условие усилено: жетон модуля атаки. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей на поле два своих добытчика с полной энергией, примыкающих к разным зарождениям, — награда бесплатная Добыча. Если оба примыкают к большим зарождениям, условие усилено: 1 монета. Своё зарождение вырабатывают все, чужое — только те, кто дотянулся.</t>
         </is>
       </c>
     </row>
@@ -2913,43 +2935,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД забери последний келемий с зарождения</t>
         </is>
       </c>
-      <c r="F3" s="2">
-        <v>3</v>
-      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mining</t>
+        </is>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ты исчерпал зарождение - оно ушло с поля</t>
         </is>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сборки</t>
-        </is>
-      </c>
-      <c r="T3" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД забери последний келемий с зарождения — награда 3 монеты. Если ты исчерпал зарождение и оно ушло с поля, условие усилено: жетон модуля сборки. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД забери последний келемий с зарождения — награда бесплатная Добыча. Если ты исчерпал зарождение и оно ушло с поля, условие усилено: 1 монета. Исчерпанное зарождение приближает конец партии — считай, кому это выгодно.</t>
         </is>
       </c>
     </row>
@@ -2979,43 +3003,45 @@
           <t xml:space="preserve">Имей одновременно ноль монет и ноль боеприпасов</t>
         </is>
       </c>
-      <c r="F4" s="2">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
-        <v>3.25</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mining</t>
+        </is>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Не имей даже келемий</t>
         </is>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
       <c r="P4" s="2"/>
-      <c r="Q4" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
-      <c r="T4" s="2">
-        <v>5.25</v>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей одновременно ноль монет и ноль боеприпасов — награда 2 монеты и 1 боеприпас. Не имей даже келемий, и условие усилено: 1 трофей. Ва-банк играют только на голом столе.</t>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей одновременно ноль монет и ноль боеприпасов — награда бесплатная Добыча. Не имей даже келемий, и условие усилено: 1 монета. Ва-банк играют только на голом столе.</t>
         </is>
       </c>
     </row>
@@ -3042,40 +3068,42 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками)</t>
-        </is>
-      </c>
-      <c r="F5" s="2">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
+          <t xml:space="preserve">В ЭТОТ ХОД забери контейнер (добытчиком или войском)</t>
+        </is>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
-        <v>3.25</v>
-      </c>
-      <c r="M5" s="2"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="T5" s="2">
-        <v>3.25</v>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД забери 3 контейнера (добытчиками или войсками) — награда 2 монеты и 1 боеприпас. Усиления у карты нет: три контейнера за ход и так работа всей смены. Каждый добытчик в Добыче выбирает одно: келемий или контейнер.</t>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД забери контейнер (добытчиком или войском) — награда бесплатный Рынок. Усиления у карты нет. Каждый добытчик в Добыче выбирает одно: келемий или контейнер, а войско берёт контейнер, войдя на его ячейку.</t>
         </is>
       </c>
     </row>
@@ -3105,43 +3133,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД произведи только боеприпасы и ни одного войска</t>
         </is>
       </c>
-      <c r="F6" s="2">
-        <v>2</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
+      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Эти здания - завод и авиабаза</t>
         </is>
       </c>
-      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="2">
+      <c r="R6" s="2"/>
+      <c r="S6" s="2">
         <v>1</v>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД произведи только боеприпасы и ни одного войска — награда 2 монеты и 1 карта задания. Если эти здания - завод и авиабаза, условие усилено: 1 карта арсенала. Ход без единого нового войска — цена полного залпа.</t>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД произведи только боеприпасы и ни одного войска — награда бесплатный Рынок. Если эти здания - завод и авиабаза, условие усилено: 1 келемий. Ход без единого нового войска — цена полного залпа.</t>
         </is>
       </c>
     </row>
@@ -3171,45 +3201,45 @@
           <t xml:space="preserve">Имей два своих войска на гексах, где нет твоих зданий</t>
         </is>
       </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combat</t>
+        </is>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Четыре - и все стоят на разных гексах</t>
         </is>
       </c>
-      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="P7" s="2">
+        <v>2</v>
+      </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сборки</t>
-        </is>
-      </c>
-      <c r="T7" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей два своих войска на гексах, где нет твоих зданий, — награда 2 монеты и 1 карта задания. Если таких войск четыре и все стоят на разных гексах, условие усилено: жетон модуля сборки. Войско без своего здания рядом умрёт первым — зато не даром.</t>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей два своих войска на гексах, где нет твоих зданий, — награда бесплатный Бой. Если таких войск четыре и все стоят на разных гексах, условие усилено: 2 боеприпаса. Войско без своего здания рядом умрёт первым — зато не даром.</t>
         </is>
       </c>
     </row>
@@ -3240,40 +3270,44 @@
         </is>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
-        <v>3.75</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combat</t>
+        </is>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Одна из вышек стоит на гексе с жетонами врага</t>
         </is>
       </c>
-      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2">
+      <c r="P8" s="2">
         <v>2</v>
       </c>
+      <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="2">
-        <v>7.75</v>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей на поле 2 свои вышки на разных гексах, и обе не на гексе с ЦУ, — награда 3 боеприпаса. Если одна из вышек стоит на гексе с жетонами врага, условие усилено: 2 трофея. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей на поле 2 свои вышки на разных гексах, и обе не на гексе с ЦУ, — награда бесплатный Бой. Если одна из вышек стоит на гексе с жетонами врага, условие усилено: 2 боеприпаса. Вышка не двигается вовсе, поэтому опорный пункт выбирают один раз и навсегда.</t>
         </is>
       </c>
     </row>
@@ -3304,40 +3338,44 @@
         </is>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="2">
-        <v>3</v>
-      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2">
-        <v>3.75</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">movement</t>
+        </is>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Держи так сразу два своих войска</t>
         </is>
       </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
+      <c r="P9" s="2">
+        <v>1</v>
+      </c>
       <c r="Q9" s="2"/>
-      <c r="R9" s="2">
-        <v>1</v>
-      </c>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="2">
-        <v>7.75</v>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага, — награда 3 боеприпаса. Держи так сразу два войска, и условие усилено: 1 карта арсенала. Гарнизон в здании не виден до первого выстрела.</t>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей военное здание с войском внутри, по соседству с гексом, где есть жетоны врага, — награда бесплатный Манёвр. Держи так сразу два войска, и условие усилено: 1 боеприпас. Гарнизон в здании не виден до первого выстрела.</t>
         </is>
       </c>
     </row>
@@ -3368,40 +3406,44 @@
         </is>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2">
-        <v>3.75</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">movement</t>
+        </is>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на одном таком гексе два своих войска</t>
         </is>
       </c>
-      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="P10" s="2">
+        <v>1</v>
+      </c>
       <c r="Q10" s="2"/>
-      <c r="R10" s="2">
-        <v>1</v>
-      </c>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="2">
-        <v>7.75</v>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей своё войско на гексе, где есть здания врага, — награда 3 боеприпаса. Имей на одном таком гексе два своих войска, и условие усилено: 1 карта арсенала. Двор чужой, а гекс общий: здание закрывает только свои стенки, и войти во двор можно, пока в нём есть свободный сектор.</t>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей своё войско на гексе, где есть здания врага, — награда бесплатный Манёвр. Имей на одном таком гексе два своих войска, и условие усилено: 1 боеприпас. Двор чужой, а гекс общий: здание закрывает только свои стенки, и войти во двор можно, пока в нём есть свободный сектор.</t>
         </is>
       </c>
     </row>
@@ -3432,42 +3474,42 @@
         </is>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="2">
-        <v>2</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2">
-        <v>4.1</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Двух видов</t>
         </is>
       </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей в запасе 0 войск одного вида — награда 2 боеприпаса и 1 карта задания. Если так стоят сразу два рода, условие усилено: 2 трофея. Вывести род целиком значит подставить его целиком: в запасе не осталось никого, кем заменить убитого.</t>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей в запасе 0 войск одного вида — награда два спец-действия в этот ход. Если так стоят сразу два рода, условие усилено: 1 карта задания. Вывести род целиком значит подставить его целиком: в запасе не осталось никого, кем заменить убитого.</t>
         </is>
       </c>
     </row>
@@ -3497,33 +3539,37 @@
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся двумя разными предложениями Рынка</t>
         </is>
       </c>
-      <c r="F12" s="2">
-        <v>3</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M12" s="2"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assembly</t>
+        </is>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся двумя разными предложениями Рынка. Награда: 3 монеты. Напечатанные курсы планшета и предложения карты рынка считаются по отдельности. Усиления у карты нет.</t>
         </is>
@@ -3555,41 +3601,45 @@
           <t xml:space="preserve">Дойди до второго шага хотя бы на одном треке технологий</t>
         </is>
       </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assembly</t>
+        </is>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Стой на втором шаге сразу на двух треках</t>
         </is>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" s="2">
+        <v>1</v>
+      </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="2">
-        <v>1</v>
-      </c>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дойди до второго шага хотя бы на одном треке технологий — награда 3 монеты. Стой на втором шаге сразу на двух треках, и условие усилено: 1 карта арсенала. Второй шаг — первое место, где трек начинает платить очками.</t>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дойди до второго шага хотя бы на одном треке технологий — награда бесплатное Снаряжение. Стой на втором шаге сразу на двух треках, и условие усилено: 1 монета. Второй шаг — первое место, где трек начинает платить очками.</t>
         </is>
       </c>
     </row>
@@ -3616,40 +3666,42 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
-        </is>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">В ЭТОТ ХОД воспользуйся двумя разными предложениями Науки</t>
+        </is>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="M14" s="2"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="T14" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки. Награда: 1 монета и 2 боеприпаса. Шаг по треку и каждый обмен трофеев на планшете технологий считаются отдельным предложением; обменов на планшете три, значит три предложения — это ровно все они за один ход. Усиления у карты нет.</t>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД воспользуйся двумя разными предложениями Науки — награда бесплатный Рынок. Шаг по треку и каждый обмен трофеев на планшете технологий считаются отдельным предложением. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -3681,39 +3733,43 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2">
-        <v>2</v>
-      </c>
+      <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На трёх треках</t>
         </is>
       </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="2">
+      <c r="R15" s="2"/>
+      <c r="S15" s="2">
         <v>1</v>
       </c>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда 2 карты задания. На трёх треках условие усилено: 1 карта арсенала. Одно действие Науки берёт сколько угодно разных треков, по шагу на каждом, — но каждый шаг оплачивается трофеями отдельно.</t>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД сдай трофеи на двух разных треках технологий — награда бесплатный Рынок. На трёх треках условие усилено: 1 келемий. Одно действие Науки берёт сколько угодно разных треков, по шагу на каждом, — но каждый шаг оплачивается трофеями отдельно.</t>
         </is>
       </c>
     </row>
@@ -3743,41 +3799,45 @@
           <t xml:space="preserve">Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника</t>
         </is>
       </c>
-      <c r="F16" s="2">
-        <v>3</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assembly</t>
+        </is>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Твоих зданий вокруг чужого ЦУ два, и стоят они на разных гексах</t>
         </is>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="O16" s="2">
+        <v>1</v>
+      </c>
       <c r="P16" s="2"/>
-      <c r="Q16" s="2">
-        <v>2</v>
-      </c>
+      <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="T16" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника, — награда 3 монеты. Если таких твоих зданий два и стоят они на разных гексах, условие усилено: 2 трофея. Подобраться стройкой к чужому штабу дороже, чем кажется: туда ещё надо дойти, и там по тебе будут бить.</t>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника, — награда бесплатное Снаряжение. Если таких твоих зданий два и стоят они на разных гексах, условие усилено: 1 монета. Подобраться стройкой к чужому штабу дороже, чем кажется: туда ещё надо дойти, и там по тебе будут бить.</t>
         </is>
       </c>
     </row>
@@ -3807,41 +3867,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД построй свое здание на гексе, соседнем с гексом, где есть войска врага</t>
         </is>
       </c>
-      <c r="F17" s="2">
-        <v>3</v>
-      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assembly</t>
+        </is>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На том же соседнем гексе есть здание врага</t>
         </is>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="O17" s="2">
+        <v>1</v>
+      </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="2">
-        <v>1</v>
-      </c>
+      <c r="R17" s="2"/>
       <c r="S17" s="2"/>
-      <c r="T17" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда 3 монеты. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 карта арсенала. Передовая база строится под огнём — потому и платит.</t>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, соседнем с гексом, где есть войска противника, — награда бесплатное Снаряжение. Построй его на гексе, соседнем с гексом, где есть здание противника, и условие усилено: 1 монета. Передовая база строится под огнём — потому и платит.</t>
         </is>
       </c>
     </row>
@@ -3871,41 +3935,45 @@
           <t xml:space="preserve">Все твои здания, требующие энергию, запитаны (не менее 3)</t>
         </is>
       </c>
-      <c r="F18" s="2">
-        <v>3</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assembly</t>
+        </is>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Не менее 4 зданий</t>
         </is>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" s="2">
+        <v>1</v>
+      </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="2">
-        <v>1</v>
-      </c>
+      <c r="R18" s="2"/>
       <c r="S18" s="2"/>
-      <c r="T18" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Все твои здания, требующие энергию, запитаны, и таких зданий не менее трёх, — награда 3 монеты. Не менее четырёх зданий — условие усилено: 1 карта арсенала. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Все твои здания, требующие энергию, запитаны, и таких зданий не менее трёх, — награда бесплатное Снаряжение. Не менее четырёх зданий — условие усилено: 1 монета. Пустая ячейка ЭНР закрывается монетой только на одно действие — на состояние это не работает.</t>
         </is>
       </c>
     </row>
@@ -3935,43 +4003,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД снеси своё здание и построй другое</t>
         </is>
       </c>
-      <c r="F19" s="2">
-        <v>2</v>
-      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2">
-        <v>1</v>
-      </c>
+      <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build</t>
+        </is>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Построенное встало на тот же гекс, где стояло снесённое</t>
         </is>
       </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="O19" s="2">
+        <v>2</v>
+      </c>
       <c r="P19" s="2"/>
-      <c r="Q19" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="T19" s="2">
-        <v>5.6</v>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД снеси своё здание и построй другое — награда 2 монеты и 1 карта задания. Если построенное встало на тот же гекс, где стояло снесённое, условие усилено: 1 трофей. Здание не переезжает: его сносят и ставят заново, и обе операции стоят действия.</t>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД снеси своё здание и построй другое — награда бесплатная Стройка. Если построенное встало на тот же гекс, где стояло снесённое, условие усилено: 2 монеты. Здание не переезжает: его сносят и ставят заново, и обе операции стоят действия.</t>
         </is>
       </c>
     </row>
@@ -4002,40 +4072,44 @@
         </is>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2">
-        <v>3</v>
-      </c>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2">
-        <v>3.75</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build</t>
+        </is>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 здания на разных и несоседних между собой гексах</t>
         </is>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" s="2">
+        <v>2</v>
+      </c>
       <c r="P20" s="2"/>
-      <c r="Q20" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="T20" s="2">
-        <v>5.75</v>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД построй 2 здания на разных гексах — награда 3 боеприпаса. Построй 3 здания на разных и несоседних между собой гексах, и условие усилено: 1 трофей. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД построй 2 здания на разных гексах — награда бесплатная Стройка. Построй 3 здания на разных и несоседних между собой гексах, и условие усилено: 2 монеты. Зона стройки растёт от твоих стенок, поэтому разъехаться дороже, чем прирасти.</t>
         </is>
       </c>
     </row>
@@ -4062,44 +4136,48 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага</t>
-        </is>
-      </c>
-      <c r="F21" s="2">
-        <v>4</v>
-      </c>
+          <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, где есть жетоны врага</t>
+        </is>
+      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">На этом гексе два и более жетонов врага</t>
-        </is>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build</t>
+        </is>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">На этом гексе стоит войско врага</t>
+        </is>
+      </c>
+      <c r="O21" s="2">
+        <v>2</v>
+      </c>
       <c r="P21" s="2"/>
-      <c r="Q21" s="2">
-        <v>2</v>
-      </c>
+      <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
-      <c r="T21" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, где стоит войско врага, — награда 4 монеты. Если на этом гексе два и более жетонов врага, условие усилено: 2 трофея. Стройка под чужим стволом — заявка, а не расчёт.</t>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД построй своё здание на гексе, где есть жетоны врага, — награда бесплатная Стройка. Если на этом гексе стоит ВОЙСКО врага, условие усилено: 2 монеты. Стройка под чужим стволом — заявка, а не расчёт.</t>
         </is>
       </c>
     </row>
@@ -4129,43 +4207,45 @@
           <t xml:space="preserve">Имей на двух зданиях - источниках энергии ровно один свободный кубик</t>
         </is>
       </c>
-      <c r="F22" s="2">
-        <v>4</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">movement</t>
+        </is>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На трех источниках энергии</t>
         </is>
       </c>
-      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
+      <c r="P22" s="2">
+        <v>1</v>
+      </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сборки</t>
-        </is>
-      </c>
-      <c r="T22" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей на двух зданиях - источниках энергии ровно один свободный кубик — награда 4 монеты. На трёх источниках энергии условие усилено: жетон модуля сборки. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному неудобно намеренно.</t>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей на двух зданиях - источниках энергии ровно один свободный кубик — награда бесплатный Манёвр. На трёх источниках энергии условие усилено: 1 боеприпас. Простой кубик лежит на своём источнике, а собрать его обратно стоит гекса в Смене энергии — держать по одному неудобно намеренно.</t>
         </is>
       </c>
     </row>
@@ -4195,41 +4275,39 @@
           <t xml:space="preserve">Сбрось карту арсенала</t>
         </is>
       </c>
-      <c r="F23" s="2">
-        <v>2</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">атаки</t>
-        </is>
-      </c>
-      <c r="L23" s="2">
-        <v>7.25</v>
-      </c>
-      <c r="M23" s="2"/>
+          <t xml:space="preserve">science</t>
+        </is>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="T23" s="2">
-        <v>7.25</v>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТВЕТНЫЙ ОГОНЬ: твоё уничтоженное войско наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сбрось карту арсенала — награда 2 монеты и 1 боеприпас и жетон модуля атаки. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сбрось карту арсенала — награда бесплатная Наука. Карта арсенала стоит места на планшете; иногда выгоднее продать её, чем искать, куда установить.</t>
         </is>
       </c>
     </row>
@@ -4259,39 +4337,39 @@
           <t xml:space="preserve">Сдай в общий запас 2 боеприпаса</t>
         </is>
       </c>
-      <c r="F24" s="2">
-        <v>2</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="2">
-        <v>1</v>
-      </c>
+      <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="M24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">science</t>
+        </is>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="T24" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сдай в общий запас 2 боеприпаса — награда 2 монеты и 1 карта задания и 1 карта арсенала. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сдай в общий запас 2 боеприпаса — награда бесплатная Наука. Остаться без патронов страшно ровно до тех пор, пока по тебе не начали стрелять.</t>
         </is>
       </c>
     </row>
@@ -4322,42 +4400,42 @@
         </is>
       </c>
       <c r="F25" s="2"/>
-      <c r="G25" s="2">
-        <v>3</v>
-      </c>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2">
-        <v>3.75</v>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Технику и/или авиацию - и с одного гекса</t>
         </is>
       </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
+      <c r="Q25" s="2">
+        <v>1</v>
+      </c>
       <c r="R25" s="2"/>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сборки</t>
-        </is>
-      </c>
-      <c r="T25" s="2">
-        <v>7.75</v>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Верни в запас 2 своих войска с поля — награда 3 боеприпаса. Если это техника и/или авиация и оба жетона с одного гекса, условие усилено: жетон модуля сборки. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Верни в запас 2 своих войска с поля — награда два спец-действия в этот ход. Если это техника и/или авиация и оба жетона с одного гекса, условие усилено: 1 карта задания. Сданные войска не считаются уничтоженными и трофеями противнику не идут.</t>
         </is>
       </c>
     </row>
@@ -4387,37 +4465,37 @@
           <t xml:space="preserve">Сдай два своих неоткрытых контейнера</t>
         </is>
       </c>
-      <c r="F26" s="2">
-        <v>3</v>
-      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2">
-        <v>2</v>
-      </c>
+      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="M26" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
-      <c r="T26" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+1 БОЕПРИПАС В ПРИКАЗ НАСТУПЛЕНИЕ</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сдай два своих неоткрытых контейнера — награда 3 монеты и 2 трофея. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сдай два своих неоткрытых контейнера — награда два спец-действия в этот ход. Контейнер стоит ровно столько, сколько в нём лежит, а лежит в нём неизвестно что.</t>
         </is>
       </c>
     </row>
@@ -4447,41 +4525,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь технику или авиацию врага</t>
         </is>
       </c>
-      <c r="F27" s="2">
-        <v>4</v>
-      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combat</t>
+        </is>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">и еще 2 жетона любого врага</t>
         </is>
       </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
+      <c r="P27" s="2">
+        <v>2</v>
+      </c>
       <c r="Q27" s="2"/>
-      <c r="R27" s="2">
-        <v>1</v>
-      </c>
+      <c r="R27" s="2"/>
       <c r="S27" s="2"/>
-      <c r="T27" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь технику или авиацию врага — награда 4 монеты. Если снял ещё два любых чужих жетона, условие усилено: карта арсенала. Техника и авиация дороже прочего и стоят дальше от чужих стен: до них ещё надо дотянуться.</t>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь технику или авиацию врага — награда бесплатный Бой. Если снял ещё два любых чужих жетона, условие усилено: 2 боеприпаса. Техника и авиация дороже прочего и стоят дальше от чужих стен: до них ещё надо дотянуться.</t>
         </is>
       </c>
     </row>
@@ -4511,43 +4593,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе</t>
         </is>
       </c>
-      <c r="F28" s="2">
-        <v>4</v>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combat</t>
+        </is>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">их на этом гексе не менее 3</t>
         </is>
       </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
+      <c r="P28" s="2">
+        <v>2</v>
+      </c>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">атаки</t>
-        </is>
-      </c>
-      <c r="T28" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе — награда 4 монеты. Если их там было не меньше трёх, условие усилено: жетон модуля атаки. Вычистить гекс целиком — работа не одного выстрела: здание закрывает гекс, и снимать приходится по очереди.</t>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь все жетоны врага на одном гексе — награда бесплатный Бой. Если их там было не меньше трёх, условие усилено: 2 боеприпаса. Вычистить гекс целиком — работа не одного выстрела: здание закрывает гекс, и снимать приходится по очереди.</t>
         </is>
       </c>
     </row>
@@ -4577,43 +4661,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь добытчик противника</t>
         </is>
       </c>
-      <c r="F29" s="2">
-        <v>4</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combat</t>
+        </is>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Этот добытчик был полностью запитан и примыкал к келемию</t>
         </is>
       </c>
-      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
+      <c r="P29" s="2">
+        <v>2</v>
+      </c>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">атаки</t>
-        </is>
-      </c>
-      <c r="T29" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь добытчик противника — награда 4 монеты. Если этот добытчик был полностью запитан и примыкал к келемию, условие усилено: жетон модуля атаки. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи — а работающий на полную вдвое дороже.</t>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь добытчик противника — награда бесплатный Бой. Если этот добытчик был полностью запитан и примыкал к келемию, условие усилено: 2 боеприпаса. Отнятый добытчик стоит сопернику всех оставшихся раундов добычи — а работающий на полную вдвое дороже.</t>
         </is>
       </c>
     </row>
@@ -4643,43 +4729,45 @@
           <t xml:space="preserve">Имей среди уничтоженных жетонов жетон врага</t>
         </is>
       </c>
-      <c r="F30" s="2">
-        <v>4</v>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">movement</t>
+        </is>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">два жетона, один из них - добытчик</t>
         </is>
       </c>
-      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
+      <c r="P30" s="2">
+        <v>1</v>
+      </c>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">атаки</t>
-        </is>
-      </c>
-      <c r="T30" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей среди уничтоженных жетонов жетон врага — награда 4 монеты. Если их два и один из них добытчик, условие усилено: жетон модуля атаки. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей среди уничтоженных жетонов жетон врага — награда бесплатный Манёвр. Если их два и один из них добытчик, условие усилено: 1 боеприпас. Снесённая экономика соседа стоит дороже снесённой казармы.</t>
         </is>
       </c>
     </row>
@@ -4709,43 +4797,45 @@
           <t xml:space="preserve">Имей среди уничтоженных жетонов два жетона врага</t>
         </is>
       </c>
-      <c r="F31" s="2">
-        <v>4</v>
-      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">movement</t>
+        </is>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Один из них — энергостанция</t>
         </is>
       </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
+      <c r="P31" s="2">
+        <v>1</v>
+      </c>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сборки</t>
-        </is>
-      </c>
-      <c r="T31" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё уничтоженное здание наносит 1 урон убийце</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей среди уничтоженных жетонов два жетона врага — награда 4 монеты. Если один из них энергостанция, условие усилено: жетон модуля сборки. Энергостанция питает всё остальное, поэтому её снос стоит противнику дороже собственной цены.</t>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей среди уничтоженных жетонов два жетона врага — награда бесплатный Манёвр. Если один из них энергостанция, условие усилено: 1 боеприпас. Энергостанция питает всё остальное, поэтому её снос стоит противнику дороже собственной цены.</t>
         </is>
       </c>
     </row>
@@ -4775,43 +4865,45 @@
           <t xml:space="preserve">Имей среди уничтоженных жетонов жетоны ДВУХ разных противников</t>
         </is>
       </c>
-      <c r="F32" s="2">
-        <v>4</v>
-      </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">science</t>
+        </is>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">И оба этих жетона — здания</t>
         </is>
       </c>
-      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сборки</t>
-        </is>
-      </c>
-      <c r="T32" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей среди уничтоженных жетонов жетоны двух разных противников — награда 4 монеты. Если оба этих жетона здания, условие усилено: жетон модуля сборки. Единственная карта колоды, которую нельзя закрыть, воюя с одним соседом.</t>
+      <c r="R32" s="2">
+        <v>2</v>
+      </c>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей среди уничтоженных жетонов жетоны двух разных противников — награда бесплатная Наука. Если оба этих жетона здания, условие усилено: 2 трофея. Единственная карта колоды, которую нельзя закрыть, воюя с одним соседом.</t>
         </is>
       </c>
     </row>
@@ -4841,43 +4933,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя</t>
         </is>
       </c>
-      <c r="F33" s="2">
-        <v>2</v>
-      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="2">
-        <v>1</v>
-      </c>
+      <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">science</t>
+        </is>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтоженный жетон был техникой или авиацией</t>
         </is>
       </c>
-      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
-      <c r="Q33" s="2">
-        <v>1</v>
-      </c>
-      <c r="R33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2">
+        <v>2</v>
+      </c>
       <c r="S33" s="2"/>
-      <c r="T33" s="2">
-        <v>5.6</v>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя, — награда 2 монеты и 1 карта задания. Если уничтоженный был техникой или авиацией, условие усилено: 1 трофей. Бить сильнейшего значит получить сдачи, и карта платит именно за это.</t>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше войск, чем у тебя, — награда бесплатная Наука. Если уничтоженный был техникой или авиацией, условие усилено: 2 трофея. Бить сильнейшего значит получить сдачи, и карта платит именно за это.</t>
         </is>
       </c>
     </row>
@@ -4907,43 +5001,43 @@
           <t xml:space="preserve">В ЭТОТ ХОД уничтожь два жетона противника</t>
         </is>
       </c>
-      <c r="F34" s="2">
-        <v>4</v>
-      </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД у одного из уничтоженных прочность была 2 или больше</t>
         </is>
       </c>
-      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
+      <c r="Q34" s="2">
+        <v>1</v>
+      </c>
       <c r="R34" s="2"/>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">атаки</t>
-        </is>
-      </c>
-      <c r="T34" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь два жетона противника — награда 4 монеты. Если у одного из них прочность была 2 или больше, условие усилено: жетон модуля атаки. Первая кровь считается по двум, а не по одному.</t>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь два жетона противника — награда два спец-действия в этот ход. Если у одного из них прочность была 2 или больше, условие усилено: 1 карта задания. Первая кровь считается по двум, а не по одному.</t>
         </is>
       </c>
     </row>
@@ -4974,24 +5068,22 @@
         </is>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="2">
-        <v>2</v>
-      </c>
-      <c r="H35" s="2">
-        <v>1</v>
-      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2">
-        <v>4.1</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД уничтоженный жетон был зданием</t>
         </is>
       </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2">
@@ -4999,17 +5091,19 @@
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
-      <c r="T35" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда 2 боеприпаса и 1 карта задания. Если уничтоженный жетон был зданием, условие усилено: 1 трофей. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон игрока, у которого на поле больше зданий, чем у тебя, — награда два спец-действия в этот ход. Если уничтоженный жетон был зданием, условие усилено: 1 карта задания. Догоняющему выгодно бить того, кто оторвался, — и это видно по столу без подсчёта очков.</t>
         </is>
       </c>
     </row>
@@ -5040,42 +5134,44 @@
         </is>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="2">
-        <v>2</v>
-      </c>
-      <c r="H36" s="2">
-        <v>1</v>
-      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2">
-        <v>4.1</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mining</t>
+        </is>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Это была энергостанция 3 или 4 уровня.</t>
         </is>
       </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
       <c r="P36" s="2"/>
-      <c r="Q36" s="2">
-        <v>2</v>
-      </c>
+      <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
-      <c r="T36" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь энергостанцию противника — награда 2 боеприпаса и 1 карта задания. Если это была энергостанция третьего или четвёртого уровня, условие усилено: 2 трофея. Крупные энергостанции стоят в глубине, и лезть за ними опасно.</t>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь энергостанцию противника — награда бесплатная Добыча. Если это была энергостанция третьего или четвёртого уровня, условие усилено: 1 монета. Крупные энергостанции стоят в глубине, и лезть за ними опасно.</t>
         </is>
       </c>
     </row>
@@ -5107,33 +5203,37 @@
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="2">
-        <v>2</v>
-      </c>
+      <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="M37" s="2"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build</t>
+        </is>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
-      <c r="T37" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей на поле все свои 4 здания энергостанций — награда 2 карты задания. Полный комплект источников на поле — лучшая мишень в партии: их нечем прикрыть и негде спрятать.</t>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей на поле все свои 4 здания энергостанций — награда бесплатная Стройка. Полный комплект источников на поле — лучшая мишень в партии: их нечем прикрыть и негде спрятать.</t>
         </is>
       </c>
     </row>
@@ -5165,33 +5265,37 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2">
-        <v>2</v>
-      </c>
+      <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="M38" s="2"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build</t>
+        </is>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2">
+        <v>0.0</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
-      <c r="T38" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Имей на поле все свои 4 здания добытчиков — награда 2 карты задания. Разложил всё, чем добываешь, — держи оборону или жги карту: у добытчика прочность один.</t>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имей на поле все свои 4 здания добытчиков — награда бесплатная Стройка. Разложил всё, чем добываешь, — держи оборону или жги карту: у добытчика прочность один.</t>
         </is>
       </c>
     </row>
@@ -5221,43 +5325,45 @@
           <t xml:space="preserve">В ЭТОТ ХОД найми два войска разных родов</t>
         </is>
       </c>
-      <c r="F39" s="2">
-        <v>2</v>
-      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2">
-        <v>1</v>
-      </c>
+      <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mining</t>
+        </is>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Среди нанятых есть авиация и нет ни одной вышки</t>
         </is>
       </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" s="2">
+        <v>1</v>
+      </c>
       <c r="P39" s="2"/>
-      <c r="Q39" s="2">
-        <v>2</v>
-      </c>
+      <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
-      <c r="T39" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">В ЭТОТ ХОД найми два войска разных родов — награда 2 монеты и 1 карта задания. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 2 трофея. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СВОБОДНЫЙ БОЙ</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В ЭТОТ ХОД найми два войска разных родов — награда бесплатная Добыча. Если среди нанятых есть авиация и нет ни одной вышки, условие усилено: 1 монета. Авиабаза требует трёх кубиков энергии — конвейер до неё ещё надо дотянуть.</t>
         </is>
       </c>
     </row>
@@ -5287,41 +5393,45 @@
           <t xml:space="preserve">Займи 4 разных гекса войсками хотя бы 2 видов</t>
         </is>
       </c>
-      <c r="F40" s="2">
-        <v>3</v>
-      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">6 гексов</t>
         </is>
       </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
-      <c r="Q40" s="2">
-        <v>2</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РИКОШЕТ: атака по твоему жетону переходит на любой другой жетон в том же гексе</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Займи 4 разных гекса войсками хотя бы 2 видов — награда 3 монеты. 6 гексов, и условие усилено: 2 трофея. Растянуться по полю выгодно и опасно разом: где тонко, там и порвут.</t>
+      <c r="S40" s="2">
+        <v>1</v>
+      </c>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Займи 4 разных гекса войсками хотя бы 2 видов — награда бесплатный Рынок. 6 гексов, и условие усилено: 1 келемий. Растянуться по полю выгодно и опасно разом: где тонко, там и порвут.</t>
         </is>
       </c>
     </row>
@@ -5352,47 +5462,49 @@
         </is>
       </c>
       <c r="F41" s="2"/>
-      <c r="G41" s="2">
-        <v>2</v>
-      </c>
-      <c r="H41" s="2">
-        <v>1</v>
-      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2">
-        <v>4.1</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">science</t>
+        </is>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">На 2 из них есть здания противника</t>
         </is>
       </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" s="2"/>
-      <c r="T41" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Займи войсками 5 разных гексов — награда 2 боеприпаса и 1 карта задания. Если на двух из них есть здания противника, условие усилено: 1 карта арсенала. Гекс с чужим зданием закрыт: стоять там можно, бить оттуда — только по зданиям и вышкам.</t>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">РЕМОНТ ГЕКСА</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Займи войсками 5 разных гексов — награда бесплатная Наука. Если на двух из них есть здания противника, условие усилено: 2 трофея. Гекс с чужим зданием закрыт: стоять там можно, бить оттуда — только по зданиям и вышкам.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V41"/>
+  <autoFilter ref="A1:X41"/>
 </worksheet>
 </file>
 
@@ -5410,8 +5522,9 @@
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="44" customWidth="1"/>
-    <col min="13" max="13" width="70" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="14" max="14" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5457,25 +5570,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта арсенала</t>
+          <t xml:space="preserve">келемий</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">жетон модуля</t>
+          <t xml:space="preserve">action</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">spec_actions</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">ОЦЕНКА награды</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Утиль</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Описание</t>
         </is>
@@ -5512,15 +5630,16 @@
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2">
         <v>3.6</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле не меньше трёх своих зданий, считая ЦУ, — награда трофей и карта задания. Считается и ЦУ, поэтому от подготовки до выполнения ровно две стройки.</t>
         </is>
@@ -5557,15 +5676,16 @@
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>3.6</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД найми войско любого рода, кроме вышки, — награда трофей и карта задания. Вышка не считается: её ЦУ собирает даром, и наймом это назвать нельзя.</t>
         </is>
@@ -5602,15 +5722,16 @@
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>3.6</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей не меньше трёх боеприпасов — награда трофей и карта задания. Порог три, а не два: один боеприпас у тебя уже есть с подготовки.</t>
         </is>
@@ -5647,15 +5768,16 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>3.6</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД воспользуйся предложением карты сделок на рынке — награда трофей и карта задания. Напечатанный курс не подходит: карта требует именно предложения карты сделок.</t>
         </is>
@@ -5692,15 +5814,16 @@
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="2">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
         <v>3.6</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле запитанное здание, стоящее не на гексе с твоим ЦУ, — награда трофей и карта задания. Энергия до соседнего гекса сама не дотянется: её надо туда перекинуть Сменой энергии.</t>
         </is>
@@ -5737,15 +5860,16 @@
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
         <v>3.6</v>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей на поле своё войско на расстоянии двух и больше гексов от гекса с твоим ЦУ — награда трофей и карта задания. Вышка неподвижна, так что выйти придётся кем-то живым.</t>
         </is>
@@ -5782,15 +5906,16 @@
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
         <v>3.6</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей не меньше трёх келемия — награда трофей и карта задания. Келемий равен победному очку, поэтому держать его дорого, а тратить жалко.</t>
         </is>
@@ -5827,15 +5952,16 @@
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2">
         <v>3.6</v>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей у себя не меньше двух неоткрытых контейнеров — награда трофей и карта задания. Вскрытый контейнер сразу уходит, так что придётся терпеть и не открывать.</t>
         </is>
@@ -5872,15 +5998,16 @@
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="2">
+      <c r="K10" s="2"/>
+      <c r="L10" s="2">
         <v>3.6</v>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Стой хотя бы на первом шаге любого трека технологий — награда трофей и карта задания. За действие Наука больше одного шага на трек не сделать, поэтому начинают все с одного и того же.</t>
         </is>
@@ -5917,15 +6044,16 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
         <v>3.6</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Имей среди уничтоженных жетонов хотя бы один жетон — награда трофей и карта задания. Трофей берут только с боя, поэтому карта платит за первый настоящий выстрел.</t>
         </is>
@@ -5962,15 +6090,16 @@
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2">
         <v>3.6</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 монета</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД получи действие с нижнего приказа своей карты приказа — награда трофей и карта задания. Нижний приказ открывается не всегда, так что карту держат до подходящего раунда.</t>
         </is>
@@ -6007,22 +6136,23 @@
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2">
+      <c r="K13" s="2"/>
+      <c r="L13" s="2">
         <v>3.6</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">+1 боеприпас</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">В ЭТОТ ХОД сыграй верхом тот же приказ, что и другой игрок, — награда трофей и карта задания. Совпавший приказ не срабатывает, так что эта карта — плата за потерянное действие.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:N13"/>
 </worksheet>
 </file>
 
